--- a/docs/specs/examples/template/openrater_workbook_template.xlsx
+++ b/docs/specs/examples/template/openrater_workbook_template.xlsx
@@ -429,7 +429,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>OpenRater — rating workbook TEMPLATE (filing-transcription-spec v1.0)</t>
+          <t>Koda Labs — rating workbook TEMPLATE (filing-transcription-spec v1.0)</t>
         </is>
       </c>
     </row>
@@ -491,7 +491,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>`python -m openrater.rates.ingest check &lt;file&gt;`.</t>
+          <t>`python -m api_lab.rates.ingest check &lt;file&gt;`.</t>
         </is>
       </c>
     </row>
